--- a/db/tablas_procesadas/Sala.xlsx
+++ b/db/tablas_procesadas/Sala.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24332"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\andre\Documents\Posgrado\Proyecto Titulacion\db\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PosGrado\Proyecto Titulacion\Timetabling\db\tablas_procesadas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F011A3F5-E5D8-4D56-BCBA-F7063594D288}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1FA1D845-F311-4FF9-9B3C-872B5CFCA67F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{4EFD96D6-CF62-4F2F-ABEF-608699C1E5F4}"/>
+    <workbookView xWindow="7620" yWindow="3135" windowWidth="28785" windowHeight="15345" xr2:uid="{4EFD96D6-CF62-4F2F-ABEF-608699C1E5F4}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="33">
   <si>
     <t>sala_id</t>
   </si>
@@ -126,10 +126,13 @@
     <t>Coral</t>
   </si>
   <si>
-    <t>D</t>
-  </si>
-  <si>
     <t>A-203</t>
+  </si>
+  <si>
+    <t>labo</t>
+  </si>
+  <si>
+    <t>false</t>
   </si>
 </sst>
 </file>
@@ -191,9 +194,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - Tema de 2022">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema de Office">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 - 2022">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -231,7 +234,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 - 2022">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -337,7 +340,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 - 2022">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -479,7 +482,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -487,15 +490,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D79BCFC4-C30E-4D9D-B83A-425F5E1FA7CE}">
-  <dimension ref="A1:C25"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:D24"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="13.5546875" customWidth="1"/>
-    <col min="3" max="3" width="14.6640625" customWidth="1"/>
-    <col min="4" max="4" width="19.88671875" customWidth="1"/>
+    <col min="1" max="1" width="13.5703125" customWidth="1"/>
+    <col min="3" max="3" width="14.7109375" customWidth="1"/>
+    <col min="4" max="4" width="19.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -505,8 +508,11 @@
       <c r="C1" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -516,8 +522,11 @@
       <c r="C2" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D2" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -527,8 +536,11 @@
       <c r="C3" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>5</v>
       </c>
@@ -538,8 +550,11 @@
       <c r="C4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D4" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>6</v>
       </c>
@@ -549,8 +564,11 @@
       <c r="C5" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D5" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>7</v>
       </c>
@@ -560,8 +578,11 @@
       <c r="C6" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D6" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>8</v>
       </c>
@@ -571,8 +592,11 @@
       <c r="C7" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D7" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>9</v>
       </c>
@@ -582,8 +606,11 @@
       <c r="C8" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D8" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>10</v>
       </c>
@@ -593,8 +620,11 @@
       <c r="C9" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D9" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>11</v>
       </c>
@@ -604,8 +634,11 @@
       <c r="C10" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D10" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>12</v>
       </c>
@@ -615,8 +648,11 @@
       <c r="C11" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D11" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>13</v>
       </c>
@@ -626,8 +662,11 @@
       <c r="C12" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D12" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>14</v>
       </c>
@@ -637,8 +676,11 @@
       <c r="C13" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D13" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>15</v>
       </c>
@@ -648,8 +690,11 @@
       <c r="C14" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D14" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>16</v>
       </c>
@@ -659,10 +704,13 @@
       <c r="C15" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D15" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B16">
         <v>25</v>
@@ -670,8 +718,11 @@
       <c r="C16" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D16" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>19</v>
       </c>
@@ -681,8 +732,11 @@
       <c r="C17" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D17" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>20</v>
       </c>
@@ -692,8 +746,11 @@
       <c r="C18" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D18" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>21</v>
       </c>
@@ -703,8 +760,11 @@
       <c r="C19" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D19" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>22</v>
       </c>
@@ -714,8 +774,11 @@
       <c r="C20" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D20" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>24</v>
       </c>
@@ -725,8 +788,11 @@
       <c r="C21" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D21" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>25</v>
       </c>
@@ -736,8 +802,11 @@
       <c r="C22" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D22" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>26</v>
       </c>
@@ -747,8 +816,11 @@
       <c r="C23" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D23" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>28</v>
       </c>
@@ -758,13 +830,8 @@
       <c r="C24" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A25" t="s">
-        <v>30</v>
-      </c>
-      <c r="B25">
-        <v>30</v>
+      <c r="D24" t="s">
+        <v>32</v>
       </c>
     </row>
   </sheetData>

--- a/db/tablas_procesadas/Sala.xlsx
+++ b/db/tablas_procesadas/Sala.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PosGrado\Proyecto Titulacion\Timetabling\db\tablas_procesadas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1FA1D845-F311-4FF9-9B3C-872B5CFCA67F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92FC68ED-656F-448E-B176-DF90809D77CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7620" yWindow="3135" windowWidth="28785" windowHeight="15345" xr2:uid="{4EFD96D6-CF62-4F2F-ABEF-608699C1E5F4}"/>
+    <workbookView xWindow="2730" yWindow="2730" windowWidth="28785" windowHeight="15345" xr2:uid="{4EFD96D6-CF62-4F2F-ABEF-608699C1E5F4}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -129,10 +129,10 @@
     <t>A-203</t>
   </si>
   <si>
-    <t>labo</t>
-  </si>
-  <si>
     <t>false</t>
+  </si>
+  <si>
+    <t>laboratorio</t>
   </si>
 </sst>
 </file>
@@ -174,8 +174,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -494,8 +495,8 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.5703125" customWidth="1"/>
-    <col min="3" max="3" width="14.7109375" customWidth="1"/>
-    <col min="4" max="4" width="19.85546875" customWidth="1"/>
+    <col min="3" max="3" width="19.85546875" customWidth="1"/>
+    <col min="4" max="4" width="14.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -506,10 +507,10 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D1" t="s">
         <v>2</v>
-      </c>
-      <c r="D1" t="s">
-        <v>31</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
@@ -520,10 +521,10 @@
         <v>25</v>
       </c>
       <c r="C2" t="s">
+        <v>31</v>
+      </c>
+      <c r="D2" t="s">
         <v>17</v>
-      </c>
-      <c r="D2" t="s">
-        <v>32</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
@@ -534,10 +535,10 @@
         <v>25</v>
       </c>
       <c r="C3" t="s">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="D3" t="s">
-        <v>32</v>
+        <v>18</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
@@ -548,10 +549,10 @@
         <v>25</v>
       </c>
       <c r="C4" t="s">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="D4" t="s">
-        <v>32</v>
+        <v>18</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
@@ -562,10 +563,10 @@
         <v>25</v>
       </c>
       <c r="C5" t="s">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="D5" t="s">
-        <v>32</v>
+        <v>18</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -576,10 +577,10 @@
         <v>33</v>
       </c>
       <c r="C6" t="s">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="D6" t="s">
-        <v>32</v>
+        <v>18</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
@@ -590,10 +591,10 @@
         <v>33</v>
       </c>
       <c r="C7" t="s">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="D7" t="s">
-        <v>32</v>
+        <v>18</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -604,10 +605,10 @@
         <v>33</v>
       </c>
       <c r="C8" t="s">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="D8" t="s">
-        <v>32</v>
+        <v>18</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
@@ -618,10 +619,10 @@
         <v>33</v>
       </c>
       <c r="C9" t="s">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="D9" t="s">
-        <v>32</v>
+        <v>18</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
@@ -632,10 +633,10 @@
         <v>33</v>
       </c>
       <c r="C10" t="s">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="D10" t="s">
-        <v>32</v>
+        <v>18</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
@@ -645,11 +646,11 @@
       <c r="B11">
         <v>33</v>
       </c>
-      <c r="C11" t="s">
-        <v>18</v>
+      <c r="C11" s="1" t="s">
+        <v>31</v>
       </c>
       <c r="D11" t="s">
-        <v>32</v>
+        <v>18</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
@@ -660,10 +661,10 @@
         <v>33</v>
       </c>
       <c r="C12" t="s">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="D12" t="s">
-        <v>32</v>
+        <v>18</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
@@ -674,10 +675,10 @@
         <v>33</v>
       </c>
       <c r="C13" t="s">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="D13" t="s">
-        <v>32</v>
+        <v>18</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
@@ -688,10 +689,10 @@
         <v>33</v>
       </c>
       <c r="C14" t="s">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="D14" t="s">
-        <v>32</v>
+        <v>18</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
@@ -702,10 +703,10 @@
         <v>33</v>
       </c>
       <c r="C15" t="s">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="D15" t="s">
-        <v>32</v>
+        <v>18</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
@@ -716,10 +717,10 @@
         <v>25</v>
       </c>
       <c r="C16" t="s">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="D16" t="s">
-        <v>32</v>
+        <v>18</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
@@ -730,10 +731,10 @@
         <v>20</v>
       </c>
       <c r="C17" t="s">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="D17" t="s">
-        <v>32</v>
+        <v>18</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
@@ -744,10 +745,10 @@
         <v>20</v>
       </c>
       <c r="C18" t="s">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="D18" t="s">
-        <v>32</v>
+        <v>18</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
@@ -758,10 +759,10 @@
         <v>20</v>
       </c>
       <c r="C19" t="s">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="D19" t="s">
-        <v>32</v>
+        <v>18</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
@@ -772,10 +773,10 @@
         <v>20</v>
       </c>
       <c r="C20" t="s">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="D20" t="s">
-        <v>32</v>
+        <v>18</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
@@ -786,10 +787,10 @@
         <v>30</v>
       </c>
       <c r="C21" t="s">
+        <v>31</v>
+      </c>
+      <c r="D21" t="s">
         <v>23</v>
-      </c>
-      <c r="D21" t="s">
-        <v>32</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
@@ -800,10 +801,10 @@
         <v>30</v>
       </c>
       <c r="C22" t="s">
+        <v>31</v>
+      </c>
+      <c r="D22" t="s">
         <v>17</v>
-      </c>
-      <c r="D22" t="s">
-        <v>32</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
@@ -814,10 +815,10 @@
         <v>200</v>
       </c>
       <c r="C23" t="s">
+        <v>31</v>
+      </c>
+      <c r="D23" t="s">
         <v>27</v>
-      </c>
-      <c r="D23" t="s">
-        <v>32</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
@@ -828,10 +829,10 @@
         <v>200</v>
       </c>
       <c r="C24" t="s">
+        <v>31</v>
+      </c>
+      <c r="D24" t="s">
         <v>29</v>
-      </c>
-      <c r="D24" t="s">
-        <v>32</v>
       </c>
     </row>
   </sheetData>
